--- a/cleaned_data/PPFAS_Portfolio_Intelligence_2016_2017_Master.xlsx
+++ b/cleaned_data/PPFAS_Portfolio_Intelligence_2016_2017_Master.xlsx
@@ -33434,7 +33434,7 @@
         <v>19155.04</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>425.7200000000011</v>
+        <v>425.7200000000012</v>
       </c>
     </row>
     <row r="46">
